--- a/artfynd/A 47330-2025 artfynd.xlsx
+++ b/artfynd/A 47330-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>132352496</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47330-2025 artfynd.xlsx
+++ b/artfynd/A 47330-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>132352496</v>
       </c>
       <c r="B3" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47330-2025 artfynd.xlsx
+++ b/artfynd/A 47330-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>132352496</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47330-2025 artfynd.xlsx
+++ b/artfynd/A 47330-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>132352496</v>
       </c>
       <c r="B3" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47330-2025 artfynd.xlsx
+++ b/artfynd/A 47330-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>130998802</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -794,11 +794,11 @@
         <v>132352496</v>
       </c>
       <c r="B3" t="n">
-        <v>57954</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -908,6 +908,366 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132352904</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ryksdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>337121</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6431423</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130998879</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ryk, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>337531</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6431441</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson, Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132352683</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ryksdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>337497</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6431494</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis ett område med cirka 10 m2.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47330-2025 artfynd.xlsx
+++ b/artfynd/A 47330-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130998802</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132352496</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134937558</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134937644</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132352904</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130998879</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,8 +1523,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132352683</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 47330-2025 artfynd.xlsx
+++ b/artfynd/A 47330-2025 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>134937558</v>
       </c>
       <c r="B4" t="n">
-        <v>58260</v>
+        <v>58265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>134937644</v>
       </c>
       <c r="B5" t="n">
-        <v>58260</v>
+        <v>58265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
